--- a/artfynd/A 43705-2022 artfynd.xlsx
+++ b/artfynd/A 43705-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43705-2022 artfynd.xlsx
+++ b/artfynd/A 43705-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>114567027</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114567033</v>
+        <v>114567028</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,7 +806,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581754</v>
+        <v>581783</v>
       </c>
       <c r="R3" t="n">
-        <v>6661858</v>
+        <v>6661855</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114567713</v>
+        <v>114567033</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,20 +910,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581749</v>
+        <v>581754</v>
       </c>
       <c r="R4" t="n">
-        <v>6661917</v>
+        <v>6661858</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +960,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -991,22 +971,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Flor Rhebergen</t>
+          <t>Mårten Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114567511</v>
+        <v>114567510</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581756</v>
+        <v>581769</v>
       </c>
       <c r="R5" t="n">
-        <v>6661887</v>
+        <v>6661862</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,15 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114567513</v>
+        <v>114567511</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,7 +1114,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1157,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581765</v>
+        <v>581756</v>
       </c>
       <c r="R6" t="n">
-        <v>6661837</v>
+        <v>6661887</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,15 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114567028</v>
+        <v>114567513</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,19 +1220,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581783</v>
+        <v>581765</v>
       </c>
       <c r="R7" t="n">
-        <v>6661855</v>
+        <v>6661837</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,6 +1277,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1319,22 +1289,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mårten Nilsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114567510</v>
+        <v>114567713</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,10 +1339,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581769</v>
+        <v>581749</v>
       </c>
       <c r="R8" t="n">
-        <v>6661862</v>
+        <v>6661917</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1395,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Flor Rhebergen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 43705-2022 artfynd.xlsx
+++ b/artfynd/A 43705-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567027</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567028</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567033</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567510</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567511</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567513</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,8 +1434,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567713</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>